--- a/app/content/qiuwei.xlsx
+++ b/app/content/qiuwei.xlsx
@@ -1066,7 +1066,7 @@
         <v>敕令责问</v>
       </c>
       <c r="C2" t="str">
-        <v>威</v>
+        <v>势</v>
       </c>
       <c r="D2" t="str">
         <v>亮出御批敕令，厉声诘其渎职拦官之罪。</v>
@@ -1077,8 +1077,8 @@
       <c r="F2">
         <v>4</v>
       </c>
-      <c r="G2">
-        <v>3</v>
+      <c r="G2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -1089,7 +1089,7 @@
         <v>冷眼威压</v>
       </c>
       <c r="C3" t="str">
-        <v>威</v>
+        <v>隐</v>
       </c>
       <c r="D3" t="str">
         <v>不发一言，只冷冷盯着他的笑。</v>
@@ -1112,7 +1112,7 @@
         <v>官场人情</v>
       </c>
       <c r="C4" t="str">
-        <v>利</v>
+        <v>势</v>
       </c>
       <c r="D4" t="str">
         <v>抬出刑部旧谊，递一句台阶。</v>
@@ -1123,8 +1123,8 @@
       <c r="F4">
         <v>2</v>
       </c>
-      <c r="G4">
-        <v>1</v>
+      <c r="G4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -1135,7 +1135,7 @@
         <v>许以好处</v>
       </c>
       <c r="C5" t="str">
-        <v>利</v>
+        <v>器</v>
       </c>
       <c r="D5" t="str">
         <v>暗示事成之后，保他考绩无忧。</v>
@@ -1158,7 +1158,7 @@
         <v>雨中体恤</v>
       </c>
       <c r="C6" t="str">
-        <v>情</v>
+        <v>策</v>
       </c>
       <c r="D6" t="str">
         <v>看他淋在雨里，递一句「辛苦」。</v>
@@ -1169,8 +1169,8 @@
       <c r="F6">
         <v>2</v>
       </c>
-      <c r="G6">
-        <v>1</v>
+      <c r="G6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1181,7 +1181,7 @@
         <v>问其家小</v>
       </c>
       <c r="C7" t="str">
-        <v>情</v>
+        <v>隐</v>
       </c>
       <c r="D7" t="str">
         <v>问他家中可有妻儿，靠谁过活。</v>
@@ -1204,7 +1204,7 @@
         <v>晓明规矩</v>
       </c>
       <c r="C8" t="str">
-        <v>理</v>
+        <v>策</v>
       </c>
       <c r="D8" t="str">
         <v>与他细论贡院出入规制、勘验条陈。</v>
@@ -1227,7 +1227,7 @@
         <v>条分利害</v>
       </c>
       <c r="C9" t="str">
-        <v>理</v>
+        <v>策</v>
       </c>
       <c r="D9" t="str">
         <v>替他算清：阻拦钦差，是灭门的罪。</v>
@@ -1238,8 +1238,8 @@
       <c r="F9">
         <v>4</v>
       </c>
-      <c r="G9">
-        <v>3</v>
+      <c r="G9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1249,6 +1249,9 @@
       <c r="B10" t="str">
         <v>墨点暗记考卷</v>
       </c>
+      <c r="C10" t="str">
+        <v>器</v>
+      </c>
       <c r="D10" t="str">
         <v>对局中亮出：右下角针尖墨点的登榜考卷——一切「文风浮躁」的官腔当场自焚。</v>
       </c>
@@ -1269,6 +1272,9 @@
       <c r="B11" t="str">
         <v>江西来路银票</v>
       </c>
+      <c r="C11" t="str">
+        <v>器</v>
+      </c>
       <c r="D11" t="str">
         <v>对局中出示：南昌藩府御用商号的票——识货的人无不色变。</v>
       </c>
@@ -1289,6 +1295,9 @@
       <c r="B12" t="str">
         <v>巡册撕页残边</v>
       </c>
+      <c r="C12" t="str">
+        <v>器</v>
+      </c>
       <c r="D12" t="str">
         <v>对局中使用：裁口笔直的档册残边拍在案上，下一言掷地有声。（成术+3）</v>
       </c>
@@ -1309,6 +1318,9 @@
       <c r="B13" t="str">
         <v>落第士子文集</v>
       </c>
+      <c r="C13" t="str">
+        <v>器</v>
+      </c>
       <c r="D13" t="str">
         <v>对局中使用：字字泣血的文章，念之心神一凛，再抽两张牌。</v>
       </c>
@@ -1329,6 +1341,9 @@
       <c r="B14" t="str">
         <v>蓑衣</v>
       </c>
+      <c r="C14" t="str">
+        <v>器</v>
+      </c>
       <c r="D14" t="str">
         <v>对局中使用：连月冷雨里的一件干蓑衣。（+3）</v>
       </c>
@@ -1349,8 +1364,11 @@
       <c r="B15" t="str">
         <v>落第士子苏砚秋</v>
       </c>
+      <c r="C15" t="str">
+        <v>势</v>
+      </c>
       <c r="D15" t="str">
-        <v>携带：情牌 +1，气力上限 +1。寒窗十二载的傲骨。</v>
+        <v>携带：策牌 +1，气力上限 +1。寒窗十二载的傲骨。</v>
       </c>
       <c r="E15" t="str">
         <v>「如今方才知晓，秋闱早已沦为权贵私器、外人棋局。」</v>
@@ -1369,6 +1387,9 @@
       <c r="B16" t="str">
         <v>书吏许安</v>
       </c>
+      <c r="C16" t="str">
+        <v>势</v>
+      </c>
       <c r="D16" t="str">
         <v>携带：气力上限 +2。位卑胆小的誊卷书吏。</v>
       </c>
@@ -1389,8 +1410,11 @@
       <c r="B17" t="str">
         <v>辅官温知予</v>
       </c>
+      <c r="C17" t="str">
+        <v>势</v>
+      </c>
       <c r="D17" t="str">
-        <v>携带：理牌 +1。谨小慎微，却把派系取舍全看在眼里。</v>
+        <v>携带：策牌 +1。谨小慎微，却把派系取舍全看在眼里。</v>
       </c>
       <c r="E17" t="str">
         <v>「科场取舍，从来无关文笔才华，只系朝堂局势。」</v>
@@ -1409,8 +1433,11 @@
       <c r="B18" t="str">
         <v>杂役陈三</v>
       </c>
+      <c r="C18" t="str">
+        <v>势</v>
+      </c>
       <c r="D18" t="str">
-        <v>携带：威牌 +1。夜夜值守库房后门的粗人。</v>
+        <v>携带：器牌 +1。夜夜值守库房后门的粗人。</v>
       </c>
       <c r="E18" t="str">
         <v>「小人虽是粗人——今年处处透着诡异。」</v>
@@ -1429,6 +1456,9 @@
       <c r="B19" t="str">
         <v>囊中碎银</v>
       </c>
+      <c r="C19" t="str">
+        <v>器</v>
+      </c>
       <c r="D19" t="str">
         <v>资源卡：翻到即入钱袋。</v>
       </c>
@@ -1448,6 +1478,9 @@
       </c>
       <c r="B20" t="str">
         <v>官驿银三十两</v>
+      </c>
+      <c r="C20" t="str">
+        <v>器</v>
       </c>
       <c r="D20" t="str">
         <v>资源卡：翻到即入钱袋。</v>
@@ -1668,7 +1701,7 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>理,威,理,理,威,情,利</v>
+        <v>策,势,策,隐,策,势,策</v>
       </c>
       <c r="I2" t="str">
         <v>w_wei_chi,w_wei_ning,w_li_guan,w_li_yi,w_qing_tong,w_qing_jia,w_li_gui,w_li_fen</v>
